--- a/data/trans_orig/P16A09-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A09-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>55165</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85409</t>
+          <t>86627</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>114943</t>
+          <t>111953</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>157034</t>
+          <t>155940</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>174459</t>
+          <t>175413</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>229209</t>
+          <t>229031</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>946314</t>
+          <t>945096</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>977225</t>
+          <t>976558</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1158079</t>
+          <t>1159173</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1200170</t>
+          <t>1203160</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2117626</t>
+          <t>2117804</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2172376</t>
+          <t>2171422</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>11793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31381</t>
+          <t>31779</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17309</t>
+          <t>18233</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38253</t>
+          <t>38803</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35182</t>
+          <t>34778</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64273</t>
+          <t>61964</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1661013</t>
+          <t>1660615</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1679268</t>
+          <t>1680601</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1549420</t>
+          <t>1548870</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1570364</t>
+          <t>1569440</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3215794</t>
+          <t>3218103</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3244885</t>
+          <t>3245289</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14557</t>
+          <t>14474</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>5901</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20781</t>
+          <t>20514</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10083</t>
+          <t>10821</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28481</t>
+          <t>29670</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>536851</t>
+          <t>536934</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>549168</t>
+          <t>549243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>455631</t>
+          <t>455898</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>470541</t>
+          <t>470511</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>999339</t>
+          <t>998150</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1017737</t>
+          <t>1016999</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77076</t>
+          <t>78300</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>115878</t>
+          <t>114764</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>147850</t>
+          <t>146473</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>199364</t>
+          <t>198455</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>235279</t>
+          <t>236178</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>298426</t>
+          <t>301417</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3159647</t>
+          <t>3160761</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3198449</t>
+          <t>3197225</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3179833</t>
+          <t>3180742</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3231347</t>
+          <t>3232724</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6356296</t>
+          <t>6353305</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6419443</t>
+          <t>6418544</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26514</t>
+          <t>27215</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52456</t>
+          <t>53747</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>141765</t>
+          <t>145301</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>190380</t>
+          <t>193749</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>178478</t>
+          <t>179361</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>232801</t>
+          <t>236947</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>919381</t>
+          <t>918090</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>945323</t>
+          <t>944622</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1141171</t>
+          <t>1137802</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1189786</t>
+          <t>1186250</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2070587</t>
+          <t>2066441</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2124910</t>
+          <t>2124027</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,21%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16497</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38133</t>
+          <t>38233</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19854</t>
+          <t>22223</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43979</t>
+          <t>45378</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42486</t>
+          <t>42861</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74284</t>
+          <t>73817</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1921889</t>
+          <t>1921789</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1943525</t>
+          <t>1943564</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1707870</t>
+          <t>1706471</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1731995</t>
+          <t>1729626</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3637587</t>
+          <t>3638054</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3669385</t>
+          <t>3669010</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16448</t>
+          <t>16588</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>2181</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13695</t>
+          <t>13723</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7088</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23658</t>
+          <t>23853</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>463884</t>
+          <t>463744</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>478235</t>
+          <t>478218</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>443959</t>
+          <t>443931</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455112</t>
+          <t>455473</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>914328</t>
+          <t>914133</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>930898</t>
+          <t>931608</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54949</t>
+          <t>54954</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92008</t>
+          <t>91355</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>179173</t>
+          <t>179614</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>235364</t>
+          <t>236150</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>244940</t>
+          <t>245850</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>310583</t>
+          <t>315385</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3320183</t>
+          <t>3320836</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3357242</t>
+          <t>3357237</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3305691</t>
+          <t>3304905</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3361882</t>
+          <t>3361441</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6642663</t>
+          <t>6637861</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6708306</t>
+          <t>6707396</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18123</t>
+          <t>18315</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37305</t>
+          <t>37818</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>75263</t>
+          <t>75699</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113183</t>
+          <t>112674</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99711</t>
+          <t>101091</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>139860</t>
+          <t>144656</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>717042</t>
+          <t>716529</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>736224</t>
+          <t>736032</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>881477</t>
+          <t>881986</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>919397</t>
+          <t>918961</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1609147</t>
+          <t>1604351</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1649296</t>
+          <t>1647916</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,22%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10573</t>
+          <t>9898</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29397</t>
+          <t>28524</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26004</t>
+          <t>26255</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52488</t>
+          <t>50786</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41389</t>
+          <t>41462</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70953</t>
+          <t>72558</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2046988</t>
+          <t>2047861</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2065812</t>
+          <t>2066487</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1935812</t>
+          <t>1937514</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1962296</t>
+          <t>1962045</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3993732</t>
+          <t>3992127</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4023296</t>
+          <t>4023223</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,82 +4640,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4205</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1069</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10597</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>4205</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>10869</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4205</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1079</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9976</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>4205</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>1073</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>9657</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>544794</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>546886</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,82 +4753,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>544935</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>538543</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>548071</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,07%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1091822</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1085158</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1095030</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>99,62%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>544935</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>539164</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>548061</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,8%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1023</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1091822</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1086370</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1094954</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,91%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32870</t>
+          <t>32613</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61020</t>
+          <t>59103</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>112952</t>
+          <t>110851</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>160305</t>
+          <t>159148</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>152363</t>
+          <t>153058</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>208598</t>
+          <t>207433</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3316598</t>
+          <t>3318515</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3344748</t>
+          <t>3345005</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3371795</t>
+          <t>3372952</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3419148</t>
+          <t>3421249</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6701120</t>
+          <t>6702285</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6757355</t>
+          <t>6756660</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17072</t>
+          <t>16365</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32701</t>
+          <t>33152</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>83709</t>
+          <t>84175</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>117043</t>
+          <t>117046</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>106480</t>
+          <t>104068</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>141280</t>
+          <t>141456</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>480035</t>
+          <t>479584</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>495664</t>
+          <t>496371</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>634689</t>
+          <t>634686</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>668023</t>
+          <t>667557</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1123188</t>
+          <t>1123012</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1157988</t>
+          <t>1160400</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22190</t>
+          <t>22946</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49184</t>
+          <t>48985</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48270</t>
+          <t>49753</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85413</t>
+          <t>85476</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>83936</t>
+          <t>80231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>127093</t>
+          <t>124995</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2241143</t>
+          <t>2241342</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2268137</t>
+          <t>2267381</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2151732</t>
+          <t>2151669</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2188875</t>
+          <t>2187392</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4400379</t>
+          <t>4402477</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4443536</t>
+          <t>4447241</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13536</t>
+          <t>13204</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27754</t>
+          <t>28110</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14286</t>
+          <t>14396</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29054</t>
+          <t>28915</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>640920</t>
+          <t>640789</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>631833</t>
+          <t>631477</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>646051</t>
+          <t>646383</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1277157</t>
+          <t>1277296</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1291925</t>
+          <t>1291815</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46382</t>
+          <t>45038</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78129</t>
+          <t>77184</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>150931</t>
+          <t>149932</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>211240</t>
+          <t>212067</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>212294</t>
+          <t>210806</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>281018</t>
+          <t>276307</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3371558</t>
+          <t>3372503</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3403305</t>
+          <t>3404649</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3437224</t>
+          <t>3436397</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3497533</t>
+          <t>3498532</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6817132</t>
+          <t>6821843</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6885856</t>
+          <t>6887344</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A09-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A09-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55165</t>
+          <t>54156</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86627</t>
+          <t>85748</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>111953</t>
+          <t>113087</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>155940</t>
+          <t>157703</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>175413</t>
+          <t>176255</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>229031</t>
+          <t>227713</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>945096</t>
+          <t>945975</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>976558</t>
+          <t>977567</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1159173</t>
+          <t>1157410</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1203160</t>
+          <t>1202026</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2117804</t>
+          <t>2119122</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2171422</t>
+          <t>2170580</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11793</t>
+          <t>12325</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31779</t>
+          <t>30587</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18233</t>
+          <t>18091</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38803</t>
+          <t>40639</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34778</t>
+          <t>35082</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61964</t>
+          <t>63942</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1660615</t>
+          <t>1661807</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1680601</t>
+          <t>1680069</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1548870</t>
+          <t>1547034</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1569440</t>
+          <t>1569582</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3218103</t>
+          <t>3216125</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3245289</t>
+          <t>3244985</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14474</t>
+          <t>14018</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20514</t>
+          <t>20054</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10821</t>
+          <t>10558</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29670</t>
+          <t>28444</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>536934</t>
+          <t>537390</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>549243</t>
+          <t>548984</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>455898</t>
+          <t>456358</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>470511</t>
+          <t>470739</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>998150</t>
+          <t>999376</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1016999</t>
+          <t>1017262</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78300</t>
+          <t>78523</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>114764</t>
+          <t>115374</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>146473</t>
+          <t>147081</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>198455</t>
+          <t>200905</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>236178</t>
+          <t>235431</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>301417</t>
+          <t>299774</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3160761</t>
+          <t>3160151</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3197225</t>
+          <t>3197002</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3180742</t>
+          <t>3178292</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3232724</t>
+          <t>3232116</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6353305</t>
+          <t>6354948</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6418544</t>
+          <t>6419291</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27215</t>
+          <t>27400</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53747</t>
+          <t>52752</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>145301</t>
+          <t>143738</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>193749</t>
+          <t>191788</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>179361</t>
+          <t>179459</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>236947</t>
+          <t>233103</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>918090</t>
+          <t>919085</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>944622</t>
+          <t>944437</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1137802</t>
+          <t>1139763</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1186250</t>
+          <t>1187813</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2066441</t>
+          <t>2070285</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2124027</t>
+          <t>2123929</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>16759</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38233</t>
+          <t>38165</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22223</t>
+          <t>21726</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45378</t>
+          <t>45744</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42861</t>
+          <t>43453</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73817</t>
+          <t>74183</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1921789</t>
+          <t>1921857</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1943564</t>
+          <t>1943263</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1706471</t>
+          <t>1706105</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1729626</t>
+          <t>1730123</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3638054</t>
+          <t>3637688</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3669010</t>
+          <t>3668418</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16588</t>
+          <t>17130</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13723</t>
+          <t>12924</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23853</t>
+          <t>24952</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>463744</t>
+          <t>463202</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>478218</t>
+          <t>478224</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>443931</t>
+          <t>444730</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455473</t>
+          <t>454675</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>914133</t>
+          <t>913034</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>931608</t>
+          <t>930825</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54954</t>
+          <t>55034</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91355</t>
+          <t>91699</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>179614</t>
+          <t>178043</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>236150</t>
+          <t>236958</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>245850</t>
+          <t>244820</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>315385</t>
+          <t>309492</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3320836</t>
+          <t>3320492</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3357237</t>
+          <t>3357157</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3304905</t>
+          <t>3304097</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3361441</t>
+          <t>3363012</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6637861</t>
+          <t>6643754</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6707396</t>
+          <t>6708426</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18315</t>
+          <t>18058</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37818</t>
+          <t>37712</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>75699</t>
+          <t>74047</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>112674</t>
+          <t>111939</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101091</t>
+          <t>100720</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144656</t>
+          <t>142925</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>716529</t>
+          <t>716635</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>736032</t>
+          <t>736289</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>881986</t>
+          <t>882721</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>918961</t>
+          <t>920613</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1604351</t>
+          <t>1606082</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1647916</t>
+          <t>1648287</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9898</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28524</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26255</t>
+          <t>25928</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50786</t>
+          <t>52393</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41462</t>
+          <t>40333</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72558</t>
+          <t>71658</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2047861</t>
+          <t>2047554</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2066487</t>
+          <t>2066146</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1937514</t>
+          <t>1935907</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1962045</t>
+          <t>1962372</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3992127</t>
+          <t>3993027</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4023223</t>
+          <t>4024352</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10597</t>
+          <t>9720</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10869</t>
+          <t>10769</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>538543</t>
+          <t>539420</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>548071</t>
+          <t>548062</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1085158</t>
+          <t>1085258</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1095030</t>
+          <t>1094938</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32613</t>
+          <t>32570</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59103</t>
+          <t>57984</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>110851</t>
+          <t>113559</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>159148</t>
+          <t>158544</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>153058</t>
+          <t>152490</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>207433</t>
+          <t>208991</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3318515</t>
+          <t>3319634</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3345005</t>
+          <t>3345048</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3372952</t>
+          <t>3373556</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3421249</t>
+          <t>3418541</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6702285</t>
+          <t>6700727</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6756660</t>
+          <t>6757228</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>23770</t>
+          <t>25337</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16365</t>
+          <t>17587</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33152</t>
+          <t>35122</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>96846</t>
+          <t>102122</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>84175</t>
+          <t>88773</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>117046</t>
+          <t>117698</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>120616</t>
+          <t>127458</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104068</t>
+          <t>110724</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>141456</t>
+          <t>145540</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>488966</t>
+          <t>550900</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>479584</t>
+          <t>541115</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>496371</t>
+          <t>558650</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>654886</t>
+          <t>717663</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>634686</t>
+          <t>702087</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>667557</t>
+          <t>731012</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1143852</t>
+          <t>1268563</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1123012</t>
+          <t>1250481</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1160400</t>
+          <t>1285297</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>92,07%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>512736</t>
+          <t>576237</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>512736</t>
+          <t>576237</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>512736</t>
+          <t>576237</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>751732</t>
+          <t>819785</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>751732</t>
+          <t>819785</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>751732</t>
+          <t>819785</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1264468</t>
+          <t>1396021</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1264468</t>
+          <t>1396021</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1264468</t>
+          <t>1396021</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35452</t>
+          <t>39157</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22946</t>
+          <t>27600</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48985</t>
+          <t>52011</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>68226</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49753</t>
+          <t>63660</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85476</t>
+          <t>93019</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>103677</t>
+          <t>115558</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80231</t>
+          <t>98988</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>124995</t>
+          <t>135632</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2254875</t>
+          <t>2191409</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2241342</t>
+          <t>2178555</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2267381</t>
+          <t>2202966</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2168919</t>
+          <t>2094306</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2151669</t>
+          <t>2077688</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2187392</t>
+          <t>2107047</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4423795</t>
+          <t>4285716</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4402477</t>
+          <t>4265642</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4447241</t>
+          <t>4302286</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>5059</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>19415</t>
+          <t>23310</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13204</t>
+          <t>16336</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28110</t>
+          <t>32958</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>24617</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14396</t>
+          <t>17356</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28915</t>
+          <t>35130</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -6336,27 +6336,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>645236</t>
+          <t>710280</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>640789</t>
+          <t>706528</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>640172</t>
+          <t>710695</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>631477</t>
+          <t>701047</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>646383</t>
+          <t>717669</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1285408</t>
+          <t>1420975</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1277296</t>
+          <t>1410462</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1291815</t>
+          <t>1428236</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>659587</t>
+          <t>734005</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>659587</t>
+          <t>734005</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>659587</t>
+          <t>734005</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1306211</t>
+          <t>1445592</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1306211</t>
+          <t>1445592</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1306211</t>
+          <t>1445592</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>60609</t>
+          <t>65800</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45038</t>
+          <t>51285</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77184</t>
+          <t>82494</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>184487</t>
+          <t>201833</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>149932</t>
+          <t>178374</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>212067</t>
+          <t>223618</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>245096</t>
+          <t>267633</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>210806</t>
+          <t>244570</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>276307</t>
+          <t>295883</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3389078</t>
+          <t>3452590</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3372503</t>
+          <t>3435896</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3404649</t>
+          <t>3467105</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3463977</t>
+          <t>3522664</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3436397</t>
+          <t>3500879</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3498532</t>
+          <t>3546123</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6853054</t>
+          <t>6975254</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6821843</t>
+          <t>6947004</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6887344</t>
+          <t>6998317</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3449687</t>
+          <t>3518390</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3449687</t>
+          <t>3518390</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3449687</t>
+          <t>3518390</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3648464</t>
+          <t>3724497</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3648464</t>
+          <t>3724497</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3648464</t>
+          <t>3724497</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7098150</t>
+          <t>7242887</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7098150</t>
+          <t>7242887</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7098150</t>
+          <t>7242887</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
